--- a/analysis/tables/gpt-j-6b.xlsx
+++ b/analysis/tables/gpt-j-6b.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9266406425914915</v>
+        <v>0.6733588669498168</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1584717239578271</v>
+        <v>-0.05963005541473465</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.927x - 0.158</t>
+          <t>y = 0.673x - 0.060</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8624775248763458</v>
+        <v>0.8624775248763452</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07719729761293938</v>
+        <v>0.07719729761293941</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1710174545276115</v>
+        <v>0.08855613008386905</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7681689186336644</v>
+        <v>0.6137288115350822</v>
       </c>
       <c r="K3" t="n">
         <v>0.1795845638119629</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9131192056502373</v>
+        <v>0.6710601490736766</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1088399977314978</v>
+        <v>-0.05332350401802377</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.913x - 0.109</t>
+          <t>y = 0.671x - 0.053</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8691138878060121</v>
+        <v>0.8646703384810646</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07691627394795067</v>
+        <v>0.07710444064861023</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1191958257563888</v>
+        <v>0.07946158640418582</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8042792079187395</v>
+        <v>0.6177366450556528</v>
       </c>
       <c r="K4" t="n">
         <v>0.1795845638119629</v>
